--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/2000000/Output_0_9.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/2000000/Output_0_9.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>320071.425633411</v>
+        <v>320074.8015362156</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547406</v>
+        <v>2995243.61350639</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745723</v>
+        <v>20355670.24425592</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4812396.678818936</v>
+        <v>4812058.022867889</v>
       </c>
     </row>
     <row r="11">
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="C8" t="n">
-        <v>10.95151064538747</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1132,19 +1132,19 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1186,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="9">
@@ -1211,16 +1211,16 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>22.15420867374215</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J9" t="n">
         <v>0.7465913262578567</v>
@@ -1247,13 +1247,13 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1296,13 +1296,13 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>23.19571111787229</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K10" t="n">
         <v>22.26949182588285</v>
@@ -1320,16 +1320,16 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2741920426674804</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1405,16 +1405,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>26</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="S11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U11" t="n">
-        <v>22.90079999999999</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>22.15420867374215</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="G12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -1533,13 +1533,13 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>23.19571111787229</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K13" t="n">
         <v>22.26949182588285</v>
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2741920426674241</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1606,16 +1606,16 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1645,16 +1645,16 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -1721,16 +1721,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U15" t="n">
-        <v>22.90079999999999</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1794,19 +1794,19 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.27419204266741</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>19.84491174912431</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1843,16 +1843,16 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1879,16 +1879,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>24.66239999999999</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>24.66239999999999</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1958,13 +1958,13 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>28</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1973,13 +1973,13 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2034,19 +2034,19 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T19" t="n">
-        <v>19.30102689107961</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>19.72731862540289</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>212.2728</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>84.41978777916125</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2113,13 +2113,13 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -2134,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="21">
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>98.14443661786946</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>131.1597968056182</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2210,13 +2210,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2308,16 +2308,16 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>52.42556848774763</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2353,13 +2353,13 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2368,10 +2368,10 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2384,13 +2384,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -2435,25 +2435,25 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.903356019873729</v>
+        <v>84.0572199420196</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2526,13 +2526,13 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2545,19 +2545,19 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>202.2821007854552</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2605,13 +2605,13 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2624,19 +2624,19 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>92.02640584743135</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2669,22 +2669,22 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>64.6171849794068</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -2748,22 +2748,22 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2791,16 +2791,16 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2833,22 +2833,22 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>230.2038249569697</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>232.8062112150493</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2861,10 +2861,10 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>109.3620287046445</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>34.66067414728059</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -2912,22 +2912,22 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X30" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2991,16 +2991,16 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3028,10 +3028,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>39.84991521806149</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3067,19 +3067,19 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="U32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>45.48281247260486</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27.00613311885778</v>
+        <v>52.93083432391725</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -3104,13 +3104,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3143,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
         <v>171.6831711038378</v>
@@ -3152,19 +3152,19 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="W33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3262,16 +3262,16 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="G35" t="n">
-        <v>29.51218284430545</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="H35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3307,10 +3307,10 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>29.85921600351676</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3380,28 +3380,28 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>140.8229710817367</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>188.9724418329533</v>
       </c>
       <c r="Y36" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3423,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>130.4655268502615</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3493,19 +3493,19 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="F38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3538,10 +3538,10 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>29.51218284430547</v>
+        <v>179.7283339446665</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -3553,7 +3553,7 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>46.99139187800655</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3617,28 +3617,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>215</v>
+        <v>132.5254342595006</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3702,10 +3702,10 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="U40" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -3727,16 +3727,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>213</v>
+        <v>187.9840913941556</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3781,13 +3781,13 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>177.6197007854552</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
     <row r="42">
@@ -3815,22 +3815,22 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>28.6611678765929</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3857,19 +3857,19 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>129.5673497550175</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="W42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -3888,67 +3888,67 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="C8" t="n">
-        <v>92.93786803496215</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D8" t="n">
-        <v>92.93786803496215</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E8" t="n">
-        <v>92.93786803496215</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F8" t="n">
-        <v>66.67524177233588</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G8" t="n">
-        <v>40.41261550970962</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H8" t="n">
-        <v>14.14998924708335</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I8" t="n">
-        <v>14.14998924708335</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K8" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L8" t="n">
-        <v>27.82</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M8" t="n">
-        <v>53.56</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="N8" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="O8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X8" t="n">
-        <v>104</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="Y8" t="n">
-        <v>104</v>
+        <v>53.80778732512771</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="C9" t="n">
-        <v>104</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="D9" t="n">
-        <v>104</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="E9" t="n">
-        <v>104</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="F9" t="n">
-        <v>81.62201144066449</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="G9" t="n">
-        <v>55.35938517803824</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="H9" t="n">
-        <v>29.09675891541198</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="I9" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K9" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L9" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M9" t="n">
-        <v>26.78000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N9" t="n">
-        <v>52.52000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O9" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P9" t="n">
-        <v>104</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R9" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S9" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="T9" t="n">
-        <v>104</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="U9" t="n">
-        <v>104</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="V9" t="n">
-        <v>104</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="W9" t="n">
-        <v>104</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="X9" t="n">
-        <v>104</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="Y9" t="n">
-        <v>104</v>
+        <v>28.6828379631348</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24.57443618776046</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="C10" t="n">
-        <v>24.57443618776046</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="D10" t="n">
-        <v>24.57443618776046</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="E10" t="n">
-        <v>24.57443618776046</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="F10" t="n">
-        <v>24.57443618776046</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="G10" t="n">
-        <v>24.57443618776046</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="H10" t="n">
-        <v>24.57443618776046</v>
+        <v>76.30222351288816</v>
       </c>
       <c r="I10" t="n">
-        <v>24.57443618776046</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="J10" t="n">
-        <v>24.57443618776046</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K10" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L10" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M10" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N10" t="n">
-        <v>79.30000000000007</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O10" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P10" t="n">
-        <v>103.3623149756393</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Q10" t="n">
-        <v>77.09968871301299</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="R10" t="n">
-        <v>50.83706245038672</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="S10" t="n">
-        <v>24.57443618776046</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="T10" t="n">
-        <v>24.57443618776046</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="U10" t="n">
-        <v>24.57443618776046</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="V10" t="n">
-        <v>24.57443618776046</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="W10" t="n">
-        <v>24.57443618776046</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="X10" t="n">
-        <v>24.57443618776046</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Y10" t="n">
-        <v>24.57443618776046</v>
+        <v>99.73223474306219</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K11" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L11" t="n">
-        <v>27.82</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M11" t="n">
-        <v>53.56</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N11" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O11" t="n">
-        <v>104</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R11" t="n">
-        <v>77.73737373737373</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="S11" t="n">
-        <v>51.47474747474747</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="T11" t="n">
-        <v>25.2121212121212</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="U11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F12" t="n">
-        <v>81.62201144066449</v>
+        <v>80.44100199269204</v>
       </c>
       <c r="G12" t="n">
-        <v>55.35938517803824</v>
+        <v>54.56191997791342</v>
       </c>
       <c r="H12" t="n">
-        <v>29.09675891541198</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="I12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K12" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L12" t="n">
-        <v>27.82</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M12" t="n">
-        <v>53.56</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N12" t="n">
-        <v>53.56</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O12" t="n">
-        <v>53.56</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P12" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.93515955286119</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="C13" t="n">
-        <v>24.93515955286119</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="D13" t="n">
-        <v>24.93515955286119</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="E13" t="n">
-        <v>24.93515955286119</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="F13" t="n">
-        <v>24.93515955286119</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="G13" t="n">
-        <v>24.93515955286119</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="H13" t="n">
-        <v>24.93515955286119</v>
+        <v>76.30222351288816</v>
       </c>
       <c r="I13" t="n">
-        <v>24.93515955286119</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="J13" t="n">
-        <v>24.93515955286119</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K13" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L13" t="n">
-        <v>28.18072336510073</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M13" t="n">
-        <v>53.92072336510073</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N13" t="n">
-        <v>79.66072336510072</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O13" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P13" t="n">
-        <v>103.72303834074</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Q13" t="n">
-        <v>77.46041207811371</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="R13" t="n">
-        <v>51.19778581548745</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="S13" t="n">
-        <v>24.93515955286119</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="T13" t="n">
-        <v>24.93515955286119</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="U13" t="n">
-        <v>24.93515955286119</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="V13" t="n">
-        <v>24.93515955286119</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="W13" t="n">
-        <v>24.93515955286119</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="X13" t="n">
-        <v>24.93515955286119</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Y13" t="n">
-        <v>24.93515955286119</v>
+        <v>99.73223474306219</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C14" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D14" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E14" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F14" t="n">
-        <v>2.08</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="G14" t="n">
-        <v>2.08</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="H14" t="n">
-        <v>2.08</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="I14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K14" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L14" t="n">
-        <v>27.82</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M14" t="n">
-        <v>53.56</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N14" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O14" t="n">
-        <v>104</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S14" t="n">
-        <v>80.86787878787879</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T14" t="n">
-        <v>54.60525252525252</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U14" t="n">
-        <v>28.34262626262626</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V14" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W14" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X14" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K15" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M15" t="n">
-        <v>26.78000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N15" t="n">
-        <v>52.52000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O15" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P15" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R15" t="n">
-        <v>77.73737373737373</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S15" t="n">
-        <v>51.47474747474747</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="T15" t="n">
-        <v>25.2121212121212</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="U15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C16" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D16" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E16" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F16" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G16" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H16" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I16" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J16" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K16" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L16" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M16" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N16" t="n">
-        <v>79.3</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O16" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P16" t="n">
-        <v>103.3623149756393</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Q16" t="n">
-        <v>77.09968871301299</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="R16" t="n">
-        <v>50.83706245038672</v>
+        <v>47.97407071350496</v>
       </c>
       <c r="S16" t="n">
-        <v>24.57443618776046</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="T16" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="U16" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V16" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W16" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X16" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y16" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="C17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="D17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="E17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="F17" t="n">
-        <v>2.24</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="H17" t="n">
-        <v>2.24</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="I17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>29.96</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L17" t="n">
-        <v>57.68</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="M17" t="n">
-        <v>84.28</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="N17" t="n">
-        <v>84.28</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O17" t="n">
-        <v>84.28</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R17" t="n">
-        <v>87.08848484848485</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S17" t="n">
-        <v>58.80565656565657</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T17" t="n">
-        <v>30.52282828282829</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="U17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="V17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="W17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="X17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27.15151515151514</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="C18" t="n">
-        <v>27.15151515151514</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="D18" t="n">
-        <v>27.15151515151514</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="E18" t="n">
-        <v>27.15151515151514</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="F18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L18" t="n">
-        <v>28.84</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="M18" t="n">
-        <v>28.84</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="N18" t="n">
-        <v>28.84</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="O18" t="n">
-        <v>56.56</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P18" t="n">
-        <v>84.28</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S18" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="T18" t="n">
-        <v>83.71717171717171</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="U18" t="n">
-        <v>83.71717171717171</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="V18" t="n">
-        <v>83.71717171717171</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="W18" t="n">
-        <v>55.43434343434343</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="X18" t="n">
-        <v>55.43434343434343</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="Y18" t="n">
-        <v>27.15151515151514</v>
+        <v>57.94462678914073</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>106.5844716071511</v>
+        <v>105.7399236434024</v>
       </c>
       <c r="Q19" t="n">
-        <v>78.30164332432284</v>
+        <v>105.7399236434024</v>
       </c>
       <c r="R19" t="n">
-        <v>50.01881504149456</v>
+        <v>77.87121125924466</v>
       </c>
       <c r="S19" t="n">
-        <v>21.73598675866627</v>
+        <v>50.00249887508694</v>
       </c>
       <c r="T19" t="n">
-        <v>2.24</v>
+        <v>22.13378649092923</v>
       </c>
       <c r="U19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>477.1313131313132</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="C20" t="n">
-        <v>477.1313131313132</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="D20" t="n">
-        <v>477.1313131313132</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="E20" t="n">
-        <v>477.1313131313132</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="F20" t="n">
-        <v>233.6969696969697</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="G20" t="n">
-        <v>19.28</v>
+        <v>104.5536560184564</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S20" t="n">
-        <v>964</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T20" t="n">
-        <v>964</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="U20" t="n">
-        <v>964</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="V20" t="n">
-        <v>964</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="W20" t="n">
-        <v>964</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="X20" t="n">
-        <v>720.5656565656566</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="Y20" t="n">
-        <v>477.1313131313132</v>
+        <v>348.0024326625565</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>178.5174550054555</v>
+        <v>485.4562706347935</v>
       </c>
       <c r="C21" t="n">
-        <v>178.5174550054555</v>
+        <v>311.0032413536665</v>
       </c>
       <c r="D21" t="n">
-        <v>178.5174550054555</v>
+        <v>311.0032413536665</v>
       </c>
       <c r="E21" t="n">
-        <v>19.28</v>
+        <v>151.765786348211</v>
       </c>
       <c r="F21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M21" t="n">
-        <v>249.2431058683491</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N21" t="n">
-        <v>473.3719638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="O21" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P21" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V21" t="n">
-        <v>728.8478917682573</v>
+        <v>728.9050472788936</v>
       </c>
       <c r="W21" t="n">
-        <v>485.4135483339139</v>
+        <v>485.4562706347935</v>
       </c>
       <c r="X21" t="n">
-        <v>485.4135483339139</v>
+        <v>485.4562706347935</v>
       </c>
       <c r="Y21" t="n">
-        <v>277.65324956896</v>
+        <v>485.4562706347935</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>506.1486868686869</v>
+        <v>559.1338160830064</v>
       </c>
       <c r="C23" t="n">
-        <v>262.7143434343434</v>
+        <v>315.6850394389064</v>
       </c>
       <c r="D23" t="n">
-        <v>262.7143434343434</v>
+        <v>315.6850394389064</v>
       </c>
       <c r="E23" t="n">
-        <v>19.28</v>
+        <v>72.23626279480629</v>
       </c>
       <c r="F23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R23" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S23" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="T23" t="n">
-        <v>749.5830303030303</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="U23" t="n">
-        <v>749.5830303030303</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="V23" t="n">
-        <v>749.5830303030303</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="W23" t="n">
-        <v>506.1486868686869</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="X23" t="n">
-        <v>506.1486868686869</v>
+        <v>559.1338160830064</v>
       </c>
       <c r="Y23" t="n">
-        <v>506.1486868686869</v>
+        <v>559.1338160830064</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>342.6674389423783</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C24" t="n">
-        <v>168.2144096612513</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L24" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M24" t="n">
-        <v>487.8331058683492</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N24" t="n">
-        <v>542.7665223866492</v>
+        <v>656.0584510084244</v>
       </c>
       <c r="O24" t="n">
-        <v>781.3565223866492</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P24" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>964</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T24" t="n">
-        <v>964</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="U24" t="n">
-        <v>962.0774181617437</v>
+        <v>705.7335281915883</v>
       </c>
       <c r="V24" t="n">
-        <v>962.0774181617437</v>
+        <v>470.5814199598456</v>
       </c>
       <c r="W24" t="n">
-        <v>718.6430747274003</v>
+        <v>227.1326433157456</v>
       </c>
       <c r="X24" t="n">
-        <v>718.6430747274003</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y24" t="n">
-        <v>510.8827759624463</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>223.6053543287427</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C26" t="n">
-        <v>223.6053543287427</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="D26" t="n">
-        <v>223.6053543287427</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="E26" t="n">
-        <v>223.6053543287427</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="F26" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S26" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T26" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U26" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V26" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W26" t="n">
-        <v>710.4740411974295</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X26" t="n">
-        <v>467.0396977630861</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y26" t="n">
-        <v>223.6053543287427</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>193.733029281127</v>
+        <v>547.1910343172051</v>
       </c>
       <c r="C27" t="n">
-        <v>19.28</v>
+        <v>547.1910343172051</v>
       </c>
       <c r="D27" t="n">
-        <v>19.28</v>
+        <v>398.2566246559538</v>
       </c>
       <c r="E27" t="n">
-        <v>19.28</v>
+        <v>305.3006591534979</v>
       </c>
       <c r="F27" t="n">
-        <v>19.28</v>
+        <v>158.7661011803829</v>
       </c>
       <c r="G27" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H27" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>144.6375600578374</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M27" t="n">
-        <v>383.2275600578374</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N27" t="n">
-        <v>621.8175600578375</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O27" t="n">
-        <v>711.9619638733197</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P27" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>689.4131260035546</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T27" t="n">
-        <v>487.2265313623206</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="U27" t="n">
-        <v>259.0029130987097</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="V27" t="n">
-        <v>193.733029281127</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="W27" t="n">
-        <v>193.733029281127</v>
+        <v>547.1910343172051</v>
       </c>
       <c r="X27" t="n">
-        <v>193.733029281127</v>
+        <v>547.1910343172051</v>
       </c>
       <c r="Y27" t="n">
-        <v>193.733029281127</v>
+        <v>547.1910343172051</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>718.7505955256626</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C29" t="n">
-        <v>718.7505955256626</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D29" t="n">
-        <v>718.7505955256626</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E29" t="n">
-        <v>718.7505955256626</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F29" t="n">
-        <v>718.7505955256626</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G29" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H29" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S29" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T29" t="n">
-        <v>953.9083846317729</v>
+        <v>738.7078125165641</v>
       </c>
       <c r="U29" t="n">
-        <v>953.9083846317729</v>
+        <v>738.7078125165641</v>
       </c>
       <c r="V29" t="n">
-        <v>953.9083846317729</v>
+        <v>495.259035872464</v>
       </c>
       <c r="W29" t="n">
-        <v>953.9083846317729</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="X29" t="n">
-        <v>953.9083846317729</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y29" t="n">
-        <v>718.7505955256626</v>
+        <v>262.7299197543128</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>304.9538575951698</v>
+        <v>55.04605772994853</v>
       </c>
       <c r="C30" t="n">
-        <v>130.5008283140428</v>
+        <v>55.04605772994853</v>
       </c>
       <c r="D30" t="n">
-        <v>20.03413265278571</v>
+        <v>55.04605772994853</v>
       </c>
       <c r="E30" t="n">
-        <v>20.03413265278571</v>
+        <v>55.04605772994853</v>
       </c>
       <c r="F30" t="n">
-        <v>20.03413265278571</v>
+        <v>55.04605772994853</v>
       </c>
       <c r="G30" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H30" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I30" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M30" t="n">
-        <v>473.3719638733197</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N30" t="n">
-        <v>711.9619638733197</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O30" t="n">
-        <v>711.9619638733197</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P30" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T30" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U30" t="n">
-        <v>964</v>
+        <v>533.6469426057913</v>
       </c>
       <c r="V30" t="n">
-        <v>964</v>
+        <v>298.4948343740486</v>
       </c>
       <c r="W30" t="n">
-        <v>720.5656565656566</v>
+        <v>55.04605772994853</v>
       </c>
       <c r="X30" t="n">
-        <v>512.7141563601238</v>
+        <v>55.04605772994853</v>
       </c>
       <c r="Y30" t="n">
-        <v>304.9538575951698</v>
+        <v>55.04605772994853</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U31" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V31" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.2</v>
+        <v>275.0536540581672</v>
       </c>
       <c r="C32" t="n">
-        <v>17.2</v>
+        <v>275.0536540581672</v>
       </c>
       <c r="D32" t="n">
-        <v>17.2</v>
+        <v>275.0536540581672</v>
       </c>
       <c r="E32" t="n">
-        <v>17.2</v>
+        <v>275.0536540581672</v>
       </c>
       <c r="F32" t="n">
-        <v>17.2</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="G32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K32" t="n">
-        <v>120.2150059109224</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L32" t="n">
-        <v>300.290857495581</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M32" t="n">
-        <v>513.1408574955809</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N32" t="n">
-        <v>621.144994565301</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O32" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q32" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R32" t="n">
-        <v>708.6170525846973</v>
+        <v>710.1930433168102</v>
       </c>
       <c r="S32" t="n">
-        <v>497.4856691642474</v>
+        <v>710.1930433168102</v>
       </c>
       <c r="T32" t="n">
-        <v>497.4856691642474</v>
+        <v>492.6233486874887</v>
       </c>
       <c r="U32" t="n">
-        <v>280.3139519925302</v>
+        <v>492.6233486874887</v>
       </c>
       <c r="V32" t="n">
-        <v>63.142234820813</v>
+        <v>492.6233486874887</v>
       </c>
       <c r="W32" t="n">
-        <v>17.2</v>
+        <v>275.0536540581672</v>
       </c>
       <c r="X32" t="n">
-        <v>17.2</v>
+        <v>275.0536540581672</v>
       </c>
       <c r="Y32" t="n">
-        <v>17.2</v>
+        <v>275.0536540581672</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.2</v>
+        <v>315.953932890268</v>
       </c>
       <c r="C33" t="n">
-        <v>17.2</v>
+        <v>315.953932890268</v>
       </c>
       <c r="D33" t="n">
-        <v>17.2</v>
+        <v>315.953932890268</v>
       </c>
       <c r="E33" t="n">
-        <v>17.2</v>
+        <v>156.7164778848125</v>
       </c>
       <c r="F33" t="n">
-        <v>17.2</v>
+        <v>156.7164778848125</v>
       </c>
       <c r="G33" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="H33" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="I33" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L33" t="n">
-        <v>17.2</v>
+        <v>230.4715775208402</v>
       </c>
       <c r="M33" t="n">
-        <v>230.05</v>
+        <v>443.7116352270382</v>
       </c>
       <c r="N33" t="n">
-        <v>442.9</v>
+        <v>443.7116352270382</v>
       </c>
       <c r="O33" t="n">
-        <v>655.75</v>
+        <v>656.9516929332361</v>
       </c>
       <c r="P33" t="n">
-        <v>790.6054414866707</v>
+        <v>839.595170546587</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R33" t="n">
-        <v>860</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="S33" t="n">
-        <v>686.5826554506689</v>
+        <v>586.9891167356675</v>
       </c>
       <c r="T33" t="n">
-        <v>686.5826554506689</v>
+        <v>586.9891167356675</v>
       </c>
       <c r="U33" t="n">
-        <v>469.4109382789517</v>
+        <v>586.9891167356675</v>
       </c>
       <c r="V33" t="n">
-        <v>469.4109382789517</v>
+        <v>369.419422106346</v>
       </c>
       <c r="W33" t="n">
-        <v>252.2392211072345</v>
+        <v>369.419422106346</v>
       </c>
       <c r="X33" t="n">
-        <v>252.2392211072345</v>
+        <v>369.419422106346</v>
       </c>
       <c r="Y33" t="n">
-        <v>44.47892234228058</v>
+        <v>369.419422106346</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="C34" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="D34" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="E34" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="F34" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="G34" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="H34" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I34" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J34" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K34" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L34" t="n">
-        <v>752.7818345174422</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M34" t="n">
-        <v>791.9698727096644</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N34" t="n">
-        <v>835.6607233651007</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O34" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P34" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q34" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R34" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S34" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T34" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="U34" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="V34" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="W34" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="X34" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Y34" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>698.5254372164702</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="C35" t="n">
-        <v>698.5254372164702</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="D35" t="n">
-        <v>698.5254372164702</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="E35" t="n">
-        <v>481.353720044753</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="F35" t="n">
-        <v>264.1820028730358</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="G35" t="n">
-        <v>234.3717171717172</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K35" t="n">
-        <v>22.36462077340309</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L35" t="n">
-        <v>202.4404723580617</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M35" t="n">
-        <v>415.2904723580617</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N35" t="n">
-        <v>621.144994565301</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O35" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q35" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R35" t="n">
-        <v>698.5254372164702</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="S35" t="n">
-        <v>698.5254372164702</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="T35" t="n">
-        <v>698.5254372164702</v>
+        <v>482.5317333192617</v>
       </c>
       <c r="U35" t="n">
-        <v>698.5254372164702</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="V35" t="n">
-        <v>698.5254372164702</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="W35" t="n">
-        <v>698.5254372164702</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="X35" t="n">
-        <v>698.5254372164702</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="Y35" t="n">
-        <v>698.5254372164702</v>
+        <v>452.3709090732851</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>191.653029281127</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="C36" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="D36" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="E36" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="F36" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="G36" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="H36" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="I36" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K36" t="n">
-        <v>17.2</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L36" t="n">
-        <v>221.45</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="M36" t="n">
-        <v>434.3</v>
+        <v>569.0691952848756</v>
       </c>
       <c r="N36" t="n">
-        <v>647.15</v>
+        <v>648.335933025915</v>
       </c>
       <c r="O36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R36" t="n">
-        <v>758.8304705528857</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S36" t="n">
-        <v>758.8304705528857</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T36" t="n">
-        <v>616.5850452177981</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U36" t="n">
-        <v>616.5850452177981</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="V36" t="n">
-        <v>399.4133280460809</v>
+        <v>426.43660147347</v>
       </c>
       <c r="W36" t="n">
-        <v>399.4133280460809</v>
+        <v>208.8669068441485</v>
       </c>
       <c r="X36" t="n">
-        <v>399.4133280460809</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="Y36" t="n">
-        <v>191.653029281127</v>
+        <v>17.98565246742797</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="C37" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="D37" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="E37" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="F37" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G37" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H37" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I37" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J37" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K37" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L37" t="n">
-        <v>752.7818345174422</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M37" t="n">
-        <v>791.9698727096644</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N37" t="n">
-        <v>835.6607233651007</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O37" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P37" t="n">
-        <v>857.2510699645388</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q37" t="n">
-        <v>857.2510699645388</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R37" t="n">
-        <v>857.2510699645388</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S37" t="n">
-        <v>857.2510699645388</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T37" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="U37" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="V37" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="W37" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="X37" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Y37" t="n">
-        <v>725.4677095097293</v>
+        <v>151.763810304913</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>451.5434343434343</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="C38" t="n">
-        <v>451.5434343434343</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="D38" t="n">
-        <v>451.5434343434343</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="E38" t="n">
-        <v>451.5434343434343</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="F38" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="G38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K38" t="n">
-        <v>120.2150059109224</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L38" t="n">
-        <v>202.4404723580617</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M38" t="n">
-        <v>415.2904723580617</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N38" t="n">
-        <v>621.144994565301</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O38" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R38" t="n">
-        <v>698.5254372164702</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="S38" t="n">
-        <v>668.7151515151515</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="T38" t="n">
-        <v>668.7151515151515</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="U38" t="n">
-        <v>668.7151515151515</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="V38" t="n">
-        <v>668.7151515151515</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="W38" t="n">
-        <v>451.5434343434343</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="X38" t="n">
-        <v>451.5434343434343</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="Y38" t="n">
-        <v>451.5434343434343</v>
+        <v>669.9406037026066</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>64.66605240202682</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="C39" t="n">
-        <v>64.66605240202682</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="D39" t="n">
-        <v>64.66605240202682</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="E39" t="n">
-        <v>64.66605240202682</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="F39" t="n">
-        <v>64.66605240202682</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="G39" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="H39" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L39" t="n">
-        <v>17.2</v>
+        <v>230.4715775208402</v>
       </c>
       <c r="M39" t="n">
-        <v>230.05</v>
+        <v>443.7116352270382</v>
       </c>
       <c r="N39" t="n">
-        <v>442.9</v>
+        <v>656.9516929332361</v>
       </c>
       <c r="O39" t="n">
-        <v>655.75</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P39" t="n">
-        <v>838.3934776133508</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R39" t="n">
-        <v>860</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="S39" t="n">
-        <v>860</v>
+        <v>586.9891167356675</v>
       </c>
       <c r="T39" t="n">
-        <v>657.813405358766</v>
+        <v>586.9891167356675</v>
       </c>
       <c r="U39" t="n">
-        <v>440.6416881870488</v>
+        <v>453.1250417260709</v>
       </c>
       <c r="V39" t="n">
-        <v>440.6416881870488</v>
+        <v>235.5553470967494</v>
       </c>
       <c r="W39" t="n">
-        <v>440.6416881870488</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="X39" t="n">
-        <v>440.6416881870488</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="Y39" t="n">
-        <v>232.8813894220949</v>
+        <v>17.98565246742797</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L40" t="n">
-        <v>44.51412500771298</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M40" t="n">
-        <v>83.70216319993516</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N40" t="n">
-        <v>127.3930138553715</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="U40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="V40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="W40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17.04</v>
+        <v>448.2340696092722</v>
       </c>
       <c r="C41" t="n">
-        <v>17.04</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="D41" t="n">
-        <v>17.04</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="E41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>120.0550059109223</v>
+        <v>17.62165426160527</v>
       </c>
       <c r="L41" t="n">
-        <v>300.1308574955809</v>
+        <v>197.6975058462639</v>
       </c>
       <c r="M41" t="n">
-        <v>511.0008574955809</v>
+        <v>408.9875268274333</v>
       </c>
       <c r="N41" t="n">
-        <v>716.8553797028203</v>
+        <v>614.8420490346726</v>
       </c>
       <c r="O41" t="n">
-        <v>852</v>
+        <v>764.0369991773207</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T41" t="n">
-        <v>662.4945454545455</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U41" t="n">
-        <v>447.3430303030303</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="V41" t="n">
-        <v>232.1915151515151</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="W41" t="n">
-        <v>232.1915151515151</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="X41" t="n">
-        <v>232.1915151515151</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Y41" t="n">
-        <v>232.1915151515151</v>
+        <v>638.1169902094293</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>535.6789554013706</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="C42" t="n">
-        <v>535.6789554013706</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D42" t="n">
-        <v>535.6789554013706</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E42" t="n">
-        <v>506.7282807785494</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F42" t="n">
-        <v>360.1937228054344</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G42" t="n">
-        <v>221.4628973880499</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H42" t="n">
-        <v>108.0937617956292</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L42" t="n">
-        <v>227.91</v>
+        <v>228.3639620705569</v>
       </c>
       <c r="M42" t="n">
-        <v>227.91</v>
+        <v>439.6539830517264</v>
       </c>
       <c r="N42" t="n">
-        <v>389.0919638733197</v>
+        <v>642.4070334882022</v>
       </c>
       <c r="O42" t="n">
-        <v>599.9619638733197</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="P42" t="n">
-        <v>782.6054414866707</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>750.8304705528857</v>
+        <v>752.5275250222574</v>
       </c>
       <c r="S42" t="n">
-        <v>750.8304705528857</v>
+        <v>579.1101804729262</v>
       </c>
       <c r="T42" t="n">
-        <v>750.8304705528857</v>
+        <v>579.1101804729262</v>
       </c>
       <c r="U42" t="n">
-        <v>750.8304705528857</v>
+        <v>448.2340696092722</v>
       </c>
       <c r="V42" t="n">
-        <v>750.8304705528857</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="W42" t="n">
-        <v>535.6789554013706</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="X42" t="n">
-        <v>535.6789554013706</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="Y42" t="n">
-        <v>535.6789554013706</v>
+        <v>17.07394108938743</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>852</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="C43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K43" t="n">
-        <v>717.4677095097293</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L43" t="n">
-        <v>744.7818345174422</v>
+        <v>44.38806609710041</v>
       </c>
       <c r="M43" t="n">
-        <v>783.9698727096644</v>
+        <v>83.57610428932259</v>
       </c>
       <c r="N43" t="n">
-        <v>827.6607233651007</v>
+        <v>127.2669549447589</v>
       </c>
       <c r="O43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="P43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Q43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="R43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="S43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="T43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="U43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="V43" t="n">
-        <v>852</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="W43" t="n">
-        <v>852</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="X43" t="n">
-        <v>852</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="Y43" t="n">
-        <v>852</v>
+        <v>17.07394108938743</v>
       </c>
     </row>
     <row r="44">
@@ -8433,19 +8433,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L8" t="n">
-        <v>261.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M8" t="n">
-        <v>256.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N8" t="n">
-        <v>254.3625585460859</v>
+        <v>253.9981915106306</v>
       </c>
       <c r="O8" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P8" t="n">
         <v>231.2329957552695</v>
@@ -8512,25 +8512,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L9" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>167.0835288715133</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N9" t="n">
-        <v>157.3417120833333</v>
+        <v>155.926839997373</v>
       </c>
       <c r="O9" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
-        <v>159.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>139.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,13 +8594,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O10" t="n">
         <v>163.0416663658825</v>
@@ -8670,22 +8670,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L11" t="n">
-        <v>261.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M11" t="n">
-        <v>256.3462332272727</v>
+        <v>254.9313611413124</v>
       </c>
       <c r="N11" t="n">
-        <v>254.3625585460859</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P11" t="n">
-        <v>231.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8749,13 +8749,13 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L12" t="n">
-        <v>164.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M12" t="n">
-        <v>168.1340339220183</v>
+        <v>166.719161836058</v>
       </c>
       <c r="N12" t="n">
         <v>131.3417120833333</v>
@@ -8764,10 +8764,10 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>158.9239023638252</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
-        <v>165.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,13 +8831,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O13" t="n">
         <v>163.0416663658825</v>
@@ -8907,22 +8907,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L14" t="n">
-        <v>261.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M14" t="n">
-        <v>256.3462332272727</v>
+        <v>254.9313611413124</v>
       </c>
       <c r="N14" t="n">
-        <v>254.3625585460859</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P14" t="n">
-        <v>231.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8986,25 +8986,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L15" t="n">
-        <v>138.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M15" t="n">
-        <v>167.0835288715133</v>
+        <v>166.719161836058</v>
       </c>
       <c r="N15" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
-        <v>165.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,13 +9068,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O16" t="n">
         <v>163.0416663658825</v>
@@ -9144,13 +9144,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>248.0898510449805</v>
+        <v>247.6798763052967</v>
       </c>
       <c r="L17" t="n">
-        <v>263.7664149699872</v>
+        <v>263.3564402303034</v>
       </c>
       <c r="M17" t="n">
-        <v>257.2149200959596</v>
+        <v>256.8215099922226</v>
       </c>
       <c r="N17" t="n">
         <v>229.4130635965909</v>
@@ -9159,7 +9159,7 @@
         <v>230.0982114216867</v>
       </c>
       <c r="P17" t="n">
-        <v>259.2329957552695</v>
+        <v>258.8230210155857</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9226,22 +9226,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
-        <v>165.423066648561</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>142.1340339220183</v>
+        <v>169.7240591823345</v>
       </c>
       <c r="N18" t="n">
-        <v>131.3417120833333</v>
+        <v>158.9317373436494</v>
       </c>
       <c r="O18" t="n">
-        <v>170.5962444444444</v>
+        <v>169.0715212093943</v>
       </c>
       <c r="P18" t="n">
-        <v>161.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
-        <v>167.9817740860215</v>
+        <v>167.5717993463377</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9396,7 +9396,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P20" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q20" t="n">
         <v>212.3149906599047</v>
@@ -9460,25 +9460,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L21" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>357.73449794694</v>
+        <v>301.2485028631349</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q21" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9703,19 +9703,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N24" t="n">
-        <v>186.8300115967677</v>
+        <v>301.2508595994748</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q24" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9937,22 +9937,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L27" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N27" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>233.6511977934164</v>
+        <v>255.9771075721939</v>
       </c>
       <c r="P27" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10092,7 +10092,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L29" t="n">
         <v>417.6612145504504</v>
@@ -10177,19 +10177,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M30" t="n">
-        <v>241.9030217474054</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N30" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O30" t="n">
-        <v>142.5962444444444</v>
+        <v>255.9771075721939</v>
       </c>
       <c r="P30" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q30" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10335,10 +10335,10 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>445.3462332272727</v>
+        <v>348.0675319949004</v>
       </c>
       <c r="N32" t="n">
-        <v>338.5081515458031</v>
+        <v>437.3469244119842</v>
       </c>
       <c r="O32" t="n">
         <v>380.8001812627454</v>
@@ -10411,22 +10411,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
-        <v>138.5543797798742</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M33" t="n">
-        <v>357.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N33" t="n">
-        <v>346.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P33" t="n">
-        <v>270.192025077634</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q33" t="n">
-        <v>210.0772877358491</v>
+        <v>162.1846227582699</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10566,13 +10566,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>225.3066397049837</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L35" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>445.3462332272727</v>
+        <v>348.0675319949004</v>
       </c>
       <c r="N35" t="n">
         <v>437.3469244119842</v>
@@ -10645,19 +10645,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L36" t="n">
-        <v>344.8675110930055</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M36" t="n">
-        <v>357.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N36" t="n">
-        <v>346.3417120833333</v>
+        <v>211.409123942969</v>
       </c>
       <c r="O36" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P36" t="n">
         <v>133.9744074143302</v>
@@ -10806,10 +10806,10 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L38" t="n">
-        <v>318.8224416842694</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>445.3462332272727</v>
+        <v>348.0675319949004</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
@@ -10885,22 +10885,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>138.5543797798742</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M39" t="n">
-        <v>357.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N39" t="n">
-        <v>346.3417120833333</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O39" t="n">
-        <v>357.5962444444444</v>
+        <v>349.2874543422998</v>
       </c>
       <c r="P39" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
-        <v>161.806544173546</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -11040,22 +11040,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>324.1454125711647</v>
+        <v>220.6430966734834</v>
       </c>
       <c r="L41" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>443.3462332272727</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O41" t="n">
-        <v>366.6079288935854</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P41" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11122,22 +11122,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>351.5543797798742</v>
+        <v>351.9786433972171</v>
       </c>
       <c r="M42" t="n">
-        <v>142.1340339220183</v>
+        <v>355.5582975393612</v>
       </c>
       <c r="N42" t="n">
-        <v>294.1517766018381</v>
+        <v>336.1427731302785</v>
       </c>
       <c r="O42" t="n">
-        <v>355.5962444444444</v>
+        <v>356.0205080617874</v>
       </c>
       <c r="P42" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q42" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -22978,10 +22978,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>382.7338416634806</v>
+        <v>357.1135504688497</v>
       </c>
       <c r="C8" t="n">
-        <v>354.3213811256201</v>
+        <v>339.6526005763767</v>
       </c>
       <c r="D8" t="n">
         <v>354.683041620683</v>
@@ -22990,19 +22990,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F8" t="n">
-        <v>380.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>389.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H8" t="n">
-        <v>313.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I8" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23044,10 +23044,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X8" t="n">
-        <v>369.731100678469</v>
+        <v>347.1647481942382</v>
       </c>
       <c r="Y8" t="n">
-        <v>386.2379386560536</v>
+        <v>360.6176474614227</v>
       </c>
     </row>
     <row r="9">
@@ -23069,16 +23069,16 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
-        <v>122.9150037196417</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I9" t="n">
-        <v>63.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -23105,13 +23105,13 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>100.1578341526431</v>
+        <v>74.5375429580123</v>
       </c>
       <c r="S9" t="n">
-        <v>171.6831711038378</v>
+        <v>146.062879909207</v>
       </c>
       <c r="T9" t="n">
-        <v>200.1647286948216</v>
+        <v>178.3449675368486</v>
       </c>
       <c r="U9" t="n">
         <v>225.9413820809748</v>
@@ -23154,13 +23154,13 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H10" t="n">
-        <v>162.2271725074396</v>
+        <v>139.0314613895673</v>
       </c>
       <c r="I10" t="n">
-        <v>155.4504749272583</v>
+        <v>129.8301837326275</v>
       </c>
       <c r="J10" t="n">
-        <v>93.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -23178,16 +23178,16 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.447248692439032</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S10" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T10" t="n">
         <v>227.9455894282815</v>
@@ -23263,16 +23263,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>123.8691179411497</v>
+        <v>127.3027654569188</v>
       </c>
       <c r="S11" t="n">
-        <v>183.0200695862453</v>
+        <v>183.3997783916145</v>
       </c>
       <c r="T11" t="n">
-        <v>197.0958495641314</v>
+        <v>197.4755583695005</v>
       </c>
       <c r="U11" t="n">
-        <v>228.4448529078365</v>
+        <v>225.7253617132057</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23306,16 +23306,16 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
-        <v>122.9150037196417</v>
+        <v>123.2494512354109</v>
       </c>
       <c r="G12" t="n">
-        <v>111.3435171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H12" t="n">
-        <v>86.23544423649646</v>
+        <v>86.61515304186563</v>
       </c>
       <c r="I12" t="n">
-        <v>63.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23391,13 +23391,13 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H13" t="n">
-        <v>162.2271725074396</v>
+        <v>139.0314613895673</v>
       </c>
       <c r="I13" t="n">
-        <v>155.4504749272583</v>
+        <v>129.8301837326275</v>
       </c>
       <c r="J13" t="n">
-        <v>93.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23415,16 +23415,16 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.447248692439088</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R13" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S13" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T13" t="n">
         <v>227.9455894282815</v>
@@ -23464,16 +23464,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F14" t="n">
-        <v>406.8760457417114</v>
+        <v>381.2557545470806</v>
       </c>
       <c r="G14" t="n">
-        <v>415.302737515135</v>
+        <v>389.6824463205042</v>
       </c>
       <c r="H14" t="n">
-        <v>339.4748021157671</v>
+        <v>313.8545109211363</v>
       </c>
       <c r="I14" t="n">
-        <v>210.4758895704059</v>
+        <v>187.9095370861751</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -23503,16 +23503,16 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S14" t="n">
-        <v>186.1192695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T14" t="n">
-        <v>197.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U14" t="n">
-        <v>225.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V14" t="n">
-        <v>301.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W14" t="n">
         <v>349.240968717413</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>74.15783415264313</v>
+        <v>74.5375429580123</v>
       </c>
       <c r="S15" t="n">
-        <v>145.6831711038378</v>
+        <v>146.062879909207</v>
       </c>
       <c r="T15" t="n">
-        <v>174.1647286948216</v>
+        <v>174.5444375001908</v>
       </c>
       <c r="U15" t="n">
-        <v>203.0405820809748</v>
+        <v>203.375029596744</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23637,7 +23637,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23652,19 +23652,19 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.447248692439102</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>60.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R16" t="n">
-        <v>151.2933913771695</v>
+        <v>151.6731001825387</v>
       </c>
       <c r="S16" t="n">
-        <v>198.0165980369723</v>
+        <v>198.3963068423414</v>
       </c>
       <c r="T16" t="n">
-        <v>227.9455894282815</v>
+        <v>208.1006776791572</v>
       </c>
       <c r="U16" t="n">
         <v>286.3190293564909</v>
@@ -23701,16 +23701,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>406.8760457417114</v>
+        <v>382.574751492425</v>
       </c>
       <c r="G17" t="n">
-        <v>415.302737515135</v>
+        <v>387.7127122548189</v>
       </c>
       <c r="H17" t="n">
-        <v>339.4748021157671</v>
+        <v>311.884776855451</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>182.8858643100898</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -23737,16 +23737,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>125.2067179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S17" t="n">
-        <v>181.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T17" t="n">
-        <v>195.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U17" t="n">
-        <v>223.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23774,13 +23774,13 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D18" t="n">
-        <v>147.4450655646388</v>
+        <v>119.8550403043226</v>
       </c>
       <c r="E18" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F18" t="n">
-        <v>120.4068123933839</v>
+        <v>117.4791871330677</v>
       </c>
       <c r="G18" t="n">
         <v>137.3435171632106</v>
@@ -23816,13 +23816,13 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>100.1578341526431</v>
+        <v>72.56780889232699</v>
       </c>
       <c r="S18" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T18" t="n">
-        <v>172.1647286948216</v>
+        <v>175.8634344455351</v>
       </c>
       <c r="U18" t="n">
         <v>225.9413820809748</v>
@@ -23831,13 +23831,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W18" t="n">
-        <v>223.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X18" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y18" t="n">
-        <v>177.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="19">
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>58.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>149.2933913771695</v>
+        <v>149.7033661168533</v>
       </c>
       <c r="S19" t="n">
-        <v>196.0165980369723</v>
+        <v>196.4265727766561</v>
       </c>
       <c r="T19" t="n">
-        <v>208.6445625372019</v>
+        <v>200.3555641679654</v>
       </c>
       <c r="U19" t="n">
-        <v>286.3190293564909</v>
+        <v>266.591710731088</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23938,13 +23938,13 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F20" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>203.029937515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H20" t="n">
-        <v>339.4748021157671</v>
+        <v>255.0550143366059</v>
       </c>
       <c r="I20" t="n">
         <v>210.4758895704059</v>
@@ -23971,13 +23971,13 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>223.0958495641314</v>
@@ -23992,10 +23992,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X20" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y20" t="n">
-        <v>145.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="21">
@@ -24005,10 +24005,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>68.38874703199788</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>147.4450655646388</v>
@@ -24017,7 +24017,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>145.0692123933839</v>
+        <v>13.90941558776564</v>
       </c>
       <c r="G21" t="n">
         <v>137.3435171632106</v>
@@ -24068,13 +24068,13 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X21" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="22">
@@ -24087,7 +24087,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C22" t="n">
-        <v>167.2468210986278</v>
+        <v>34.05985351325981</v>
       </c>
       <c r="D22" t="n">
         <v>148.6154730182124</v>
@@ -24138,7 +24138,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T22" t="n">
-        <v>94.75862184291347</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U22" t="n">
         <v>286.3190293564909</v>
@@ -24166,16 +24166,16 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C23" t="n">
-        <v>124.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D23" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>140.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F23" t="n">
-        <v>406.8760457417114</v>
+        <v>354.4504772539638</v>
       </c>
       <c r="G23" t="n">
         <v>415.302737515135</v>
@@ -24211,13 +24211,13 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
-        <v>20.81374877867617</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U23" t="n">
         <v>251.3456529078365</v>
@@ -24226,10 +24226,10 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W23" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X23" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y23" t="n">
         <v>386.2379386560536</v>
@@ -24242,13 +24242,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
         <v>157.6450804554009</v>
@@ -24293,25 +24293,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
-        <v>224.0380260611011</v>
+        <v>141.8841621389552</v>
       </c>
       <c r="V24" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="25">
@@ -24384,13 +24384,13 @@
         <v>252.137643323828</v>
       </c>
       <c r="W25" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X25" t="n">
         <v>225.7096553890372</v>
       </c>
       <c r="Y25" t="n">
-        <v>85.39768576672677</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="26">
@@ -24403,19 +24403,19 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C26" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D26" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E26" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F26" t="n">
-        <v>204.5939449562562</v>
+        <v>194.5906600982693</v>
       </c>
       <c r="G26" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H26" t="n">
         <v>339.4748021157671</v>
@@ -24445,7 +24445,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
         <v>149.8691179411497</v>
@@ -24463,13 +24463,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W26" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X26" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="27">
@@ -24482,19 +24482,19 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>65.6186746079696</v>
       </c>
       <c r="F27" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>112.2354442364965</v>
@@ -24503,7 +24503,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -24527,22 +24527,22 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>168.1834021700185</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X27" t="n">
         <v>205.7729852034775</v>
@@ -24606,7 +24606,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R28" t="n">
-        <v>44.10642379180149</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S28" t="n">
         <v>224.0165980369723</v>
@@ -24621,7 +24621,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W28" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X28" t="n">
         <v>225.7096553890372</v>
@@ -24649,16 +24649,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F29" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G29" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H29" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J29" t="n">
         <v>11.94928935461252</v>
@@ -24682,7 +24682,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
         <v>149.8691179411497</v>
@@ -24691,22 +24691,22 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W29" t="n">
-        <v>349.240968717413</v>
+        <v>119.0371437604433</v>
       </c>
       <c r="X29" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>153.4317274410043</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="30">
@@ -24719,10 +24719,10 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
-        <v>38.08303685999422</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E30" t="n">
         <v>157.6450804554009</v>
@@ -24731,7 +24731,7 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3435171632106</v>
+        <v>102.68284301593</v>
       </c>
       <c r="H30" t="n">
         <v>112.2354442364965</v>
@@ -24770,22 +24770,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T30" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -24849,7 +24849,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T31" t="n">
-        <v>94.7586218429135</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U31" t="n">
         <v>286.3190293564909</v>
@@ -24858,7 +24858,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W31" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X31" t="n">
         <v>225.7096553890372</v>
@@ -24886,10 +24886,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F32" t="n">
-        <v>406.8760457417114</v>
+        <v>367.02613052365</v>
       </c>
       <c r="G32" t="n">
-        <v>415.302737515135</v>
+        <v>199.9087398321068</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
@@ -24925,19 +24925,19 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>223.0958495641314</v>
+        <v>7.701851881103124</v>
       </c>
       <c r="U32" t="n">
-        <v>36.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
-        <v>112.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
-        <v>303.7581562448082</v>
+        <v>133.8469710343848</v>
       </c>
       <c r="X32" t="n">
         <v>369.731100678469</v>
@@ -24953,7 +24953,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>139.5270505310096</v>
+        <v>113.6023493259501</v>
       </c>
       <c r="C33" t="n">
         <v>172.7084989883157</v>
@@ -24962,13 +24962,13 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>112.2354442364965</v>
@@ -24977,7 +24977,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25001,7 +25001,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -25010,19 +25010,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>10.94138208097482</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
-        <v>232.8005871494253</v>
+        <v>17.40658946639704</v>
       </c>
       <c r="W33" t="n">
-        <v>36.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X33" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="34">
@@ -25050,7 +25050,7 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H34" t="n">
-        <v>162.2271725074396</v>
+        <v>29.04020492207155</v>
       </c>
       <c r="I34" t="n">
         <v>155.4504749272583</v>
@@ -25083,7 +25083,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S34" t="n">
-        <v>90.82963045160426</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T34" t="n">
         <v>227.9455894282815</v>
@@ -25120,16 +25120,16 @@
         <v>354.683041620683</v>
       </c>
       <c r="E35" t="n">
-        <v>166.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F35" t="n">
-        <v>191.8760457417114</v>
+        <v>191.4820480586832</v>
       </c>
       <c r="G35" t="n">
-        <v>385.7905546708296</v>
+        <v>199.9087398321068</v>
       </c>
       <c r="H35" t="n">
-        <v>124.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I35" t="n">
         <v>210.4758895704059</v>
@@ -25165,10 +25165,10 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T35" t="n">
-        <v>223.0958495641314</v>
+        <v>7.701851881103124</v>
       </c>
       <c r="U35" t="n">
-        <v>251.3456529078365</v>
+        <v>221.4864369043197</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25193,7 +25193,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
         <v>147.4450655646388</v>
@@ -25214,7 +25214,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25238,28 +25238,28 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
-        <v>59.34175761308489</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9413820809748</v>
+        <v>10.54738439794659</v>
       </c>
       <c r="V36" t="n">
-        <v>17.80058714942527</v>
+        <v>17.40658946639704</v>
       </c>
       <c r="W36" t="n">
-        <v>251.6949831609196</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>16.80054337052414</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="37">
@@ -25281,7 +25281,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F37" t="n">
-        <v>145.4210480229312</v>
+        <v>12.23408043756322</v>
       </c>
       <c r="G37" t="n">
         <v>167.9909793584588</v>
@@ -25311,7 +25311,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q37" t="n">
         <v>86.16204325169439</v>
@@ -25323,7 +25323,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T37" t="n">
-        <v>97.48006257802004</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U37" t="n">
         <v>286.3190293564909</v>
@@ -25351,19 +25351,19 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C38" t="n">
-        <v>365.2728917710076</v>
+        <v>149.8788940879793</v>
       </c>
       <c r="D38" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
-        <v>381.9303700722618</v>
+        <v>166.5363723892335</v>
       </c>
       <c r="F38" t="n">
-        <v>191.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>200.302737515135</v>
+        <v>199.9087398321068</v>
       </c>
       <c r="H38" t="n">
         <v>339.4748021157671</v>
@@ -25396,10 +25396,10 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>179.5078867419399</v>
+        <v>29.29173564157887</v>
       </c>
       <c r="T38" t="n">
         <v>223.0958495641314</v>
@@ -25411,7 +25411,7 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W38" t="n">
-        <v>134.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X38" t="n">
         <v>369.731100678469</v>
@@ -25427,7 +25427,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
         <v>172.7084989883157</v>
@@ -25442,7 +25442,7 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>90.3521252852041</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
         <v>112.2354442364965</v>
@@ -25451,7 +25451,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -25475,28 +25475,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>10.94138208097482</v>
+        <v>93.41594782147419</v>
       </c>
       <c r="V39" t="n">
-        <v>232.8005871494253</v>
+        <v>17.40658946639704</v>
       </c>
       <c r="W39" t="n">
-        <v>251.6949831609196</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X39" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -25560,10 +25560,10 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T40" t="n">
-        <v>227.9455894282815</v>
+        <v>94.75862184291347</v>
       </c>
       <c r="U40" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25585,16 +25585,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>169.7338416634806</v>
+        <v>194.749750269325</v>
       </c>
       <c r="C41" t="n">
-        <v>365.2728917710076</v>
+        <v>151.8486281536646</v>
       </c>
       <c r="D41" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E41" t="n">
-        <v>381.9303700722618</v>
+        <v>168.5061064549189</v>
       </c>
       <c r="F41" t="n">
         <v>406.8760457417114</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25639,13 +25639,13 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T41" t="n">
-        <v>45.47614877867616</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U41" t="n">
-        <v>38.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>114.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
         <v>349.240968717413</v>
@@ -25654,7 +25654,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y41" t="n">
-        <v>386.2379386560536</v>
+        <v>172.8136750387107</v>
       </c>
     </row>
     <row r="42">
@@ -25673,22 +25673,22 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
-        <v>128.983912578808</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25715,19 +25715,19 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9413820809748</v>
+        <v>96.37403232595733</v>
       </c>
       <c r="V42" t="n">
-        <v>232.8005871494253</v>
+        <v>19.37632353208235</v>
       </c>
       <c r="W42" t="n">
-        <v>38.69498316091961</v>
+        <v>38.27071954357669</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
@@ -25746,7 +25746,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C43" t="n">
-        <v>34.05985351325984</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D43" t="n">
         <v>148.6154730182124</v>
@@ -25806,7 +25806,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W43" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X43" t="n">
         <v>225.7096553890372</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350350.0795405005</v>
+        <v>350035.0587549795</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350350.0795405005</v>
+        <v>350035.0587549793</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350350.0795405005</v>
+        <v>350035.0587549793</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351994.6487060301</v>
+        <v>351669.2246312143</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205642</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205642</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488007.1404845364</v>
+        <v>488291.6158105898</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488007.1404845364</v>
+        <v>488291.6158105898</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488007.1404845364</v>
+        <v>488291.6158105898</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486563.0948045364</v>
+        <v>486869.422826439</v>
       </c>
     </row>
     <row r="16">
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>48378.33248915087</v>
+      </c>
+      <c r="C2" t="n">
         <v>48378.33248915088</v>
       </c>
-      <c r="C2" t="n">
-        <v>48378.33248915087</v>
-      </c>
       <c r="D2" t="n">
-        <v>51690.99534204105</v>
+        <v>51644.51686548873</v>
       </c>
       <c r="E2" t="n">
-        <v>51690.99534204106</v>
+        <v>51644.51686548873</v>
       </c>
       <c r="F2" t="n">
-        <v>51690.99534204105</v>
+        <v>51644.51686548874</v>
       </c>
       <c r="G2" t="n">
-        <v>51933.63669433229</v>
+        <v>51885.6233062447</v>
       </c>
       <c r="H2" t="n">
-        <v>74770.78047411186</v>
+        <v>74772.30263909959</v>
       </c>
       <c r="I2" t="n">
-        <v>74770.78047411186</v>
+        <v>74772.30263909958</v>
       </c>
       <c r="J2" t="n">
-        <v>74770.78047411186</v>
+        <v>74772.30263909959</v>
       </c>
       <c r="K2" t="n">
-        <v>74770.78047411186</v>
+        <v>74772.30263909957</v>
       </c>
       <c r="L2" t="n">
-        <v>72001.05351411186</v>
+        <v>72043.0252835296</v>
       </c>
       <c r="M2" t="n">
-        <v>72001.05351411186</v>
+        <v>72043.0252835296</v>
       </c>
       <c r="N2" t="n">
-        <v>72001.05351411185</v>
+        <v>72043.0252835296</v>
       </c>
       <c r="O2" t="n">
-        <v>71787.99759411186</v>
+        <v>71833.19353176959</v>
       </c>
       <c r="P2" t="n">
-        <v>48378.33248915087</v>
+        <v>48378.33248915088</v>
       </c>
     </row>
     <row r="3">
@@ -26319,7 +26319,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>7958.431053788175</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>539.8745613933579</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26371,40 +26371,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>22.532822180663</v>
+        <v>22.21667432804715</v>
       </c>
       <c r="E4" t="n">
-        <v>22.532822180663</v>
+        <v>22.21667432804714</v>
       </c>
       <c r="F4" t="n">
-        <v>22.532822180663</v>
+        <v>22.21667432804714</v>
       </c>
       <c r="G4" t="n">
-        <v>24.1832752112465</v>
+        <v>23.85668684891895</v>
       </c>
       <c r="H4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="I4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="J4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="K4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="L4" t="n">
-        <v>160.6823863208583</v>
+        <v>160.9678794298453</v>
       </c>
       <c r="M4" t="n">
-        <v>160.6823863208583</v>
+        <v>160.9678794298453</v>
       </c>
       <c r="N4" t="n">
-        <v>160.6823863208583</v>
+        <v>160.9678794298453</v>
       </c>
       <c r="O4" t="n">
-        <v>159.2331741996462</v>
+        <v>159.5405981880675</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26423,40 +26423,40 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>35185.31370463355</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26475,43 +26475,43 @@
         <v>14750.73248915088</v>
       </c>
       <c r="D6" t="n">
-        <v>8383.682519860391</v>
+        <v>8478.555432738955</v>
       </c>
       <c r="E6" t="n">
-        <v>50087.66251986039</v>
+        <v>50064.58648652713</v>
       </c>
       <c r="F6" t="n">
-        <v>50087.66251986039</v>
+        <v>50064.58648652714</v>
       </c>
       <c r="G6" t="n">
-        <v>49658.88341912104</v>
+        <v>49644.4185221752</v>
       </c>
       <c r="H6" t="n">
-        <v>2469.141330215243</v>
+        <v>2355.314235302274</v>
       </c>
       <c r="I6" t="n">
-        <v>59938.45833021525</v>
+        <v>59939.10137763394</v>
       </c>
       <c r="J6" t="n">
-        <v>59938.45833021525</v>
+        <v>59939.10137763395</v>
       </c>
       <c r="K6" t="n">
-        <v>59938.45833021525</v>
+        <v>59939.10137763392</v>
       </c>
       <c r="L6" t="n">
-        <v>58768.371127791</v>
+        <v>58786.10234497163</v>
       </c>
       <c r="M6" t="n">
-        <v>58768.371127791</v>
+        <v>58786.10234497163</v>
       </c>
       <c r="N6" t="n">
-        <v>58768.37112779099</v>
+        <v>58786.10234497163</v>
       </c>
       <c r="O6" t="n">
-        <v>58678.36441991221</v>
+        <v>58697.45770564708</v>
       </c>
       <c r="P6" t="n">
-        <v>48378.33248915087</v>
+        <v>48378.33248915088</v>
       </c>
     </row>
   </sheetData>
@@ -26733,40 +26733,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26950,43 +26950,43 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27191,7 +27191,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -35088,19 +35088,19 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N8" t="n">
-        <v>24.94949494949495</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -35167,25 +35167,25 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>24.94949494949496</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N9" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35249,13 +35249,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N10" t="n">
-        <v>26.00000000000006</v>
+        <v>25.62029119463084</v>
       </c>
       <c r="O10" t="n">
         <v>24.58512791403967</v>
@@ -35325,22 +35325,22 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M11" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N11" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35404,13 +35404,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M12" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -35419,10 +35419,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35486,13 +35486,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O13" t="n">
         <v>24.58512791403967</v>
@@ -35562,22 +35562,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M14" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N14" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35641,25 +35641,25 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M15" t="n">
-        <v>24.94949494949496</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35723,13 +35723,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O16" t="n">
         <v>24.58512791403967</v>
@@ -35799,13 +35799,13 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M17" t="n">
-        <v>26.86868686868687</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -35814,7 +35814,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35881,22 +35881,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>26.86868686868687</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O18" t="n">
-        <v>28</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="P18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36051,7 +36051,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P20" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36115,25 +36115,25 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L21" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>226.3927858636066</v>
+        <v>169.9067907798016</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q21" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36358,19 +36358,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N24" t="n">
-        <v>55.48829951343436</v>
+        <v>169.9091475161415</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36592,22 +36592,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>91.05495334897201</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="P27" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36747,7 +36747,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L29" t="n">
         <v>181.8947995804632</v>
@@ -36759,7 +36759,7 @@
         <v>207.9338608153932</v>
       </c>
       <c r="O29" t="n">
-        <v>150.7019698410586</v>
+        <v>150.7019698410587</v>
       </c>
       <c r="P29" t="n">
         <v>90.5657124162131</v>
@@ -36832,19 +36832,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M30" t="n">
-        <v>99.76898782538704</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="P30" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36990,10 +36990,10 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>215</v>
+        <v>117.7212987676277</v>
       </c>
       <c r="N32" t="n">
-        <v>109.0950879492122</v>
+        <v>207.9338608153932</v>
       </c>
       <c r="O32" t="n">
         <v>150.7019698410586</v>
@@ -37066,22 +37066,22 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M33" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P33" t="n">
-        <v>136.2176176633037</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q33" t="n">
-        <v>70.09551364982758</v>
+        <v>22.20284867224837</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37221,13 +37221,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>5.216788660003122</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L35" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>215</v>
+        <v>117.7212987676277</v>
       </c>
       <c r="N35" t="n">
         <v>207.9338608153932</v>
@@ -37300,19 +37300,19 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L36" t="n">
-        <v>206.3131313131313</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N36" t="n">
-        <v>215</v>
+        <v>80.06741185963574</v>
       </c>
       <c r="O36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -37461,10 +37461,10 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L38" t="n">
-        <v>83.05602671428214</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>215</v>
+        <v>117.7212987676277</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
@@ -37540,22 +37540,22 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O39" t="n">
-        <v>215</v>
+        <v>206.6912098978553</v>
       </c>
       <c r="P39" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>21.82477008752445</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37695,22 +37695,22 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>104.0555615261842</v>
+        <v>0.5532456285028686</v>
       </c>
       <c r="L41" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
         <v>207.9338608153932</v>
       </c>
       <c r="O41" t="n">
-        <v>136.5097174718987</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37777,22 +37777,22 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N42" t="n">
-        <v>162.8100645185048</v>
+        <v>204.8010610469452</v>
       </c>
       <c r="O42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P42" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
